--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589853.6595215225</v>
+        <v>589854</v>
       </c>
       <c r="R2" t="n">
-        <v>6359915.165439229</v>
+        <v>6359915</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-06-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106944</v>
+        <v>106950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106950</v>
+        <v>106957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106961</v>
+        <v>106969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106972</v>
+        <v>106977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106977</v>
+        <v>106985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32836-2025 artfynd.xlsx
+++ b/artfynd/A 32836-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75143815</v>
       </c>
       <c r="B2" t="n">
-        <v>106985</v>
+        <v>106995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
